--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486754_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486754_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.6348</v>
+        <v>11.0282</v>
       </c>
       <c r="E2" t="n">
-        <v>11.3534</v>
+        <v>10.1193</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2814</v>
+        <v>0.9089</v>
       </c>
       <c r="G2" t="n">
         <v>11.2733</v>
@@ -610,13 +610,13 @@
         <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1997</v>
+        <v>1.5931</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0404</v>
+        <v>0.8063</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1592</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>0.2856</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9543</v>
+        <v>3.4648</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2452</v>
+        <v>2.6316</v>
       </c>
       <c r="F3" t="n">
-        <v>0.709</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>1.4834</v>
@@ -688,13 +688,13 @@
         <v>1.7377</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4822</v>
+        <v>1.9928</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2335</v>
+        <v>1.6199</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2487</v>
+        <v>0.3728</v>
       </c>
       <c r="V3" t="n">
         <v>-1.5559</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. FORTES SILVA</t>
+          <t>G. CAMPOS MARCOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8534</v>
+        <v>3.4485</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8498</v>
+        <v>-0.2348</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0036</v>
+        <v>3.6832</v>
       </c>
       <c r="G4" t="n">
-        <v>2.671</v>
+        <v>3.6648</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3319</v>
+        <v>1.5443</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3391</v>
+        <v>2.1205</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8579</v>
+        <v>2.4175</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1254</v>
+        <v>0.9932</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7325</v>
+        <v>1.4242</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1869</v>
+        <v>1.2474</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2065</v>
+        <v>0.5511</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3934</v>
+        <v>0.6962</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-1.7377</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9654</v>
+        <v>-3.0892</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1824</v>
+        <v>0.5793</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3863</v>
+        <v>0.1514</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5687</v>
+        <v>0.4278</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.9421</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6565</v>
+        <v>0.2856</v>
       </c>
       <c r="X4" t="n">
         <v>0.6565</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. RELAÑO LOPEZ</t>
+          <t>A. FORTES SILVA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5216</v>
+        <v>3.0298</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2759</v>
+        <v>1.3738</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2457</v>
+        <v>1.6559</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2766</v>
+        <v>2.671</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.51</v>
+        <v>2.3319</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7867</v>
+        <v>0.3391</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0779</v>
+        <v>2.8579</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5091</v>
+        <v>2.1254</v>
       </c>
       <c r="L5" t="n">
-        <v>1.587</v>
+        <v>0.7325</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8012</v>
+        <v>-0.1869</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0009</v>
+        <v>0.2065</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8003</v>
+        <v>-0.3934</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1931</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1585</v>
+        <v>-0.9654</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3515</v>
+        <v>0.9654</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6078</v>
+        <v>0.3588</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3991</v>
+        <v>0.1378</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2087</v>
+        <v>0.221</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5559</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0426</v>
+        <v>-0.6565</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5133</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. CAMPOS MARCOS</t>
+          <t>A. GUERRERO PAEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3009</v>
+        <v>2.8144</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9105</v>
+        <v>2.2321</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2114</v>
+        <v>0.5823</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6648</v>
+        <v>-0.8477</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5443</v>
+        <v>-0.4137</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1205</v>
+        <v>-0.434</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4175</v>
+        <v>0.4157</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9932</v>
+        <v>-0.8956</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4242</v>
+        <v>1.3113</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2474</v>
+        <v>-1.2634</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5511</v>
+        <v>0.4819</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6962</v>
+        <v>-1.7453</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.7377</v>
+        <v>0.7723</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.0892</v>
+        <v>-0.1931</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3515</v>
+        <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5683</v>
+        <v>1.0482</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5243</v>
+        <v>0.4962</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.044</v>
+        <v>0.5521</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9421</v>
+        <v>1.8415</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2856</v>
+        <v>1.5133</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6565</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GUERRERO PAEZ</t>
+          <t>A. RELAÑO LOPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4793</v>
+        <v>1.1204</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2943</v>
+        <v>1.2968</v>
       </c>
       <c r="F7" t="n">
-        <v>0.185</v>
+        <v>-0.1764</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8477</v>
+        <v>0.2766</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4137</v>
+        <v>-0.51</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.434</v>
+        <v>0.7867</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4157</v>
+        <v>1.0779</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8956</v>
+        <v>-0.5091</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3113</v>
+        <v>1.587</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2634</v>
+        <v>-0.8012</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4819</v>
+        <v>-0.0009</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7453</v>
+        <v>-0.8003</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7723</v>
+        <v>0.1931</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1931</v>
+        <v>-1.1585</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2868</v>
+        <v>2.2066</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4416</v>
+        <v>1.42</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1547</v>
+        <v>0.7866</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8415</v>
+        <v>-1.5559</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5133</v>
+        <v>-0.0426</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3282</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1011</v>
+        <v>0.0272</v>
       </c>
       <c r="E8" t="n">
-        <v>0.109</v>
+        <v>0.2124</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.21</v>
+        <v>-0.1852</v>
       </c>
       <c r="G8" t="n">
         <v>0.5087</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0385</v>
+        <v>0.0897</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0552</v>
+        <v>0.0482</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0167</v>
+        <v>0.0415</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5712</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0152</v>
+        <v>-0.7821</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9058</v>
+        <v>-0.7472</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1093</v>
+        <v>-0.0349</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3407</v>
@@ -1156,13 +1156,13 @@
         <v>0.5792</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2537</v>
+        <v>-0.0206</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1655</v>
+        <v>-0.0069</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0881</v>
+        <v>-0.0136</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1263</v>
+        <v>-0.9484</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7385</v>
+        <v>-0.635</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3878</v>
+        <v>-0.3133</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8904</v>
@@ -1234,13 +1234,13 @@
         <v>0.1931</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1434</v>
+        <v>0.0345</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1104</v>
+        <v>-0.0069</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.033</v>
+        <v>0.0414</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2856</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.859</v>
+        <v>-2.034</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8108</v>
+        <v>1.6109</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.6698</v>
+        <v>-3.645</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2377</v>
@@ -1312,13 +1312,13 @@
         <v>0.7723</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3128</v>
+        <v>1.1377</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1858</v>
+        <v>0.9859</v>
       </c>
       <c r="U11" t="n">
-        <v>0.127</v>
+        <v>0.1519</v>
       </c>
       <c r="V11" t="n">
         <v>-2.741</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6499</v>
+        <v>-2.0735</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7969</v>
+        <v>-3.1212</v>
       </c>
       <c r="F12" t="n">
-        <v>1.147</v>
+        <v>1.0477</v>
       </c>
       <c r="G12" t="n">
         <v>-2.3734</v>
@@ -1390,13 +1390,13 @@
         <v>1.1585</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3144</v>
+        <v>0.262</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3036</v>
+        <v>0.3722</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0108</v>
+        <v>-0.1101</v>
       </c>
       <c r="V12" t="n">
         <v>2.741</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.5682</v>
+        <v>-2.8428</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.5525</v>
+        <v>-0.8767</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0157</v>
+        <v>-1.966</v>
       </c>
       <c r="G13" t="n">
         <v>-1.6013</v>
@@ -1468,13 +1468,13 @@
         <v>0.5792</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.353</v>
+        <v>0.3723</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0551</v>
+        <v>0.7308</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4081</v>
+        <v>-0.3584</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2277</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>15.4246</v>
+        <v>16.2525</v>
       </c>
       <c r="E14" t="n">
-        <v>13.0342</v>
+        <v>13.862</v>
       </c>
       <c r="F14" t="n">
-        <v>2.390499999999999</v>
+        <v>2.390400000000001</v>
       </c>
       <c r="G14" t="n">
         <v>12.5866</v>
@@ -1546,13 +1546,13 @@
         <v>11.5846</v>
       </c>
       <c r="S14" t="n">
-        <v>8.8268</v>
+        <v>9.654400000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>5.927</v>
+        <v>6.754900000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>2.8997</v>
+        <v>2.8998</v>
       </c>
       <c r="V14" t="n">
         <v>-2.1271</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8303</v>
+        <v>4.0813</v>
       </c>
       <c r="E15" t="n">
         <v>1.7718</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0585</v>
+        <v>2.3094</v>
       </c>
       <c r="G15" t="n">
         <v>2.3709</v>
@@ -1624,13 +1624,13 @@
         <v>2.1239</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9268</v>
+        <v>-0.6758</v>
       </c>
       <c r="T15" t="n">
         <v>-0.4142</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.2616</v>
       </c>
       <c r="V15" t="n">
         <v>1.2277</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0528</v>
+        <v>1.3674</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6281</v>
+        <v>2.9042</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5754</v>
+        <v>-1.5368</v>
       </c>
       <c r="G16" t="n">
         <v>0.0196</v>
@@ -1702,13 +1702,13 @@
         <v>2.3169</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4852</v>
+        <v>-0.2001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7993</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.314</v>
+        <v>-0.2754</v>
       </c>
       <c r="V16" t="n">
         <v>2.1271</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MIJE BENITEZ</t>
+          <t>A. GARCIA BORREGO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9818</v>
+        <v>-0.2139</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.0797</v>
+        <v>1.4565</v>
       </c>
       <c r="F17" t="n">
-        <v>1.098</v>
+        <v>-1.6704</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.2672</v>
+        <v>-1.0886</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2543</v>
+        <v>-0.0419</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0128</v>
+        <v>-1.0468</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.7623</v>
+        <v>1.9476</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.8053</v>
+        <v>0.442</v>
       </c>
       <c r="L17" t="n">
-        <v>0.043</v>
+        <v>1.5056</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5048</v>
+        <v>-3.0362</v>
       </c>
       <c r="N17" t="n">
-        <v>0.551</v>
+        <v>-0.4838</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0558</v>
+        <v>-2.5524</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5446</v>
+        <v>1.1585</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R17" t="n">
-        <v>2.51</v>
+        <v>2.1239</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5722</v>
+        <v>-1.4688</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5797</v>
+        <v>-0.7108</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9923999999999999</v>
+        <v>-0.758</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3129</v>
+        <v>1.1851</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2277</v>
+        <v>1.1851</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0852</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GARCIA BORREGO</t>
+          <t>M. MIJE BENITEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3267</v>
+        <v>-0.6026</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7325</v>
+        <v>-1.9763</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0592</v>
+        <v>1.3738</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0886</v>
+        <v>-2.2672</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0419</v>
+        <v>-1.2543</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0468</v>
+        <v>-1.0128</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9476</v>
+        <v>-1.7623</v>
       </c>
       <c r="K18" t="n">
-        <v>0.442</v>
+        <v>-1.8053</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5056</v>
+        <v>0.043</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.0362</v>
+        <v>-0.5048</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4838</v>
+        <v>0.551</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.5524</v>
+        <v>-1.0558</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1585</v>
+        <v>1.5446</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1239</v>
+        <v>2.51</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.5816</v>
+        <v>-1.1929</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.4347</v>
+        <v>-0.4763</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1469</v>
+        <v>-0.7167</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1851</v>
+        <v>1.3129</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1851</v>
+        <v>1.2277</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.0852</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5077</v>
+        <v>-1.0292</v>
       </c>
       <c r="E19" t="n">
-        <v>2.186</v>
+        <v>2.2894</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.6937</v>
+        <v>-3.3186</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2456</v>
@@ -1936,13 +1936,13 @@
         <v>1.9308</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2854</v>
+        <v>-0.8069</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4142</v>
+        <v>-0.3107</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8713</v>
+        <v>-0.4962</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9421</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3468</v>
+        <v>-2.4503</v>
       </c>
       <c r="E20" t="n">
-        <v>1.9233</v>
+        <v>1.4062</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.2702</v>
+        <v>-3.8565</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6903</v>
@@ -2014,13 +2014,13 @@
         <v>1.7377</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7724</v>
+        <v>-0.8759</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2753</v>
+        <v>-0.2418</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0477</v>
+        <v>-0.6341</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6565</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.2031</v>
+        <v>-6.0708</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.9461</v>
+        <v>-3.7393</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.257</v>
+        <v>-2.3315</v>
       </c>
       <c r="G21" t="n">
         <v>-4.1675</v>
@@ -2092,13 +2092,13 @@
         <v>0.1931</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2979</v>
+        <v>-0.1656</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4415</v>
+        <v>-0.2346</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1435</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.941599999999999</v>
+        <v>-8.4382</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.6063</v>
+        <v>-6.5029</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3352</v>
+        <v>-1.9353</v>
       </c>
       <c r="G22" t="n">
         <v>-5.518</v>
@@ -2170,13 +2170,13 @@
         <v>2.51</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8757</v>
+        <v>-1.3723</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6901</v>
+        <v>-0.5867</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1856</v>
+        <v>-0.7856</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1271</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-15.4246</v>
+        <v>-13.3563</v>
       </c>
       <c r="E23" t="n">
         <v>-2.390400000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-13.0342</v>
+        <v>-10.9659</v>
       </c>
       <c r="G23" t="n">
         <v>-12.5867</v>
@@ -2248,13 +2248,13 @@
         <v>15.4463</v>
       </c>
       <c r="S23" t="n">
-        <v>-8.826800000000002</v>
+        <v>-6.7583</v>
       </c>
       <c r="T23" t="n">
         <v>-2.8998</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.927</v>
+        <v>-3.8586</v>
       </c>
       <c r="V23" t="n">
         <v>2.1271</v>
